--- a/Datos_Centro.xlsx
+++ b/Datos_Centro.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,45 +444,55 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Latitud del Predio</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Longitud del Predio</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Puntaje_CULTURAL_PEDAGOGICO</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Puntaje_RIESGO_TERRITORIAL</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Puntaje_RIESGO_ESTRUCTURAL</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Puntaje_DEFICIT_COBERTURA</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Puntaje_DEFICIT_CUALITATIVO</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Puntaje_INSTALACIONES_TECNICAS</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Puntaje_ACCESIBILIDAD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Puntaje_CONFORT_AMBIENTAL</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Puntaje_TOTAL</t>
         </is>
@@ -513,30 +523,36 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.456737</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-76.591731</v>
+      </c>
+      <c r="H2" t="n">
         <v>47.17702827586207</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>24.5</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>16.317</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>29.4</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>46.33750000000001</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>41.09</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>16.3268</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>27.64354103448276</v>
       </c>
     </row>
@@ -565,30 +581,36 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>2.436926</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-76.851727</v>
+      </c>
+      <c r="H3" t="n">
         <v>65.16765034482759</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>65.91499999999999</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>16.317</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>29.4</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>51.81</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>51.2</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>74.8034</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>44.32663129310345</v>
       </c>
     </row>
@@ -617,30 +639,36 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.37984674591</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-76.4387581039</v>
+      </c>
+      <c r="H4" t="n">
         <v>47.66901793103449</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>67.75</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>22.2</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>16.317</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>29.4</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>43.395</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>71.63</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>70.1386</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>46.06245224137931</v>
       </c>
     </row>
@@ -669,30 +697,36 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.388739831</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-76.43801477</v>
+      </c>
+      <c r="H5" t="n">
         <v>63.9901951724138</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>67.75</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>22.2</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>16.317</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>29.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>36.575</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>73.19</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>70.4718</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>47.48674939655173</v>
       </c>
     </row>
@@ -721,30 +755,36 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.446218117739</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-76.48432970597401</v>
+      </c>
+      <c r="H6" t="n">
         <v>47.54926896551725</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>67.75</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>45.65000000000001</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>32.634</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>29.4</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>34.595</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>70.25999999999999</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>82.8002</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>51.32980862068966</v>
       </c>
     </row>
@@ -773,30 +813,36 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.43700417829</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-76.8516921108</v>
+      </c>
+      <c r="H7" t="n">
         <v>41.23136620689655</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>74.25</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>48.09999999999999</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>32.634</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>59</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>44.88</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>55.56</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>65.80699999999999</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>52.68279577586206</v>
       </c>
     </row>
@@ -825,30 +871,36 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.3260610622318</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-76.49991241244599</v>
+      </c>
+      <c r="H8" t="n">
         <v>63.90227241379311</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>58.375</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>35.15</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>36.7965</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>56.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>44.88</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>67.09999999999999</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>69.97199999999999</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>54.08447155172414</v>
       </c>
     </row>
@@ -877,30 +929,36 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>2.44167735929</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-76.8331819048</v>
+      </c>
+      <c r="H9" t="n">
         <v>46.19711310344828</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>30.75</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>55.90000000000001</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>65.934</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>59</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>34.6225</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>54.81</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>87.1318</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>54.29317663793104</v>
       </c>
     </row>
@@ -929,30 +987,36 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.35126153</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-76.38865666</v>
+      </c>
+      <c r="H10" t="n">
         <v>64.62563172413793</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>74.25</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>22.2</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>16.317</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>29.4</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>49.6925</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>78.23</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>99.95999999999999</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>54.33439146551724</v>
       </c>
     </row>
@@ -981,30 +1045,36 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.437008</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-76.85180099999999</v>
+      </c>
+      <c r="H11" t="n">
         <v>42.42215862068966</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>30.75</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>76.10000000000001</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>74.25900000000001</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>64.2</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>39.4075</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>62.65999999999999</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>49.147</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>54.8682073275862</v>
       </c>
     </row>
@@ -1033,30 +1103,36 @@
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.20363766127</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-76.49644309270001</v>
+      </c>
+      <c r="H12" t="n">
         <v>63.82282137931035</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>61.5</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>48.09999999999999</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>63.04689</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>64.2</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>18.2875</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>58.81</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>61.642</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>54.9261514224138</v>
       </c>
     </row>
@@ -1085,30 +1161,36 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.43583397697</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-76.8417533433</v>
+      </c>
+      <c r="H13" t="n">
         <v>47.77216689655173</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>30.75</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>55.90000000000001</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>65.934</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>64.2</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>38.72</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>49.84</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>87.1318</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>55.03099586206897</v>
       </c>
     </row>
@@ -1137,30 +1219,36 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.328999338</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-76.46921551</v>
+      </c>
+      <c r="H14" t="n">
         <v>48.8045151724138</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>33.875</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>40.59999999999999</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>74.4255</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>61.60000000000001</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>39.325</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>65.63</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>78.6352</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>55.36190189655172</v>
       </c>
     </row>
@@ -1189,30 +1277,36 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.2291317</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-76.4502134</v>
+      </c>
+      <c r="H15" t="n">
         <v>60.65496896551725</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>67.75</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>48.09999999999999</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>32.634</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>61.7</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>46.255</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>68.645</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>70.1386</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>56.98469612068965</v>
       </c>
     </row>
@@ -1241,30 +1335,36 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.343932</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-76.49567</v>
+      </c>
+      <c r="H16" t="n">
         <v>42.83704413793104</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>67.75</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>48.09999999999999</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>78.58799999999999</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>71.80000000000001</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>44.1375</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>68.63</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>40.81699999999999</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>57.83244301724138</v>
       </c>
     </row>
@@ -1293,30 +1393,36 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>2.461069</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-76.458904</v>
+      </c>
+      <c r="H17" t="n">
         <v>68.91329724137931</v>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
         <v>61.5</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>42.95</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>49.617</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>69.2</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>49.665</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>61.02</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>65.807</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>58.58403715517242</v>
       </c>
     </row>
@@ -1345,30 +1451,36 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.4105144</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-76.5754814</v>
+      </c>
+      <c r="H18" t="n">
         <v>46.67994413793104</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>74.5</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>48.09999999999999</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>82.917</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>44.2</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>27.28</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>66.81999999999999</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>82.8002</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>59.16214301724138</v>
       </c>
     </row>
@@ -1397,30 +1509,36 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.454614</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-76.41789799999999</v>
+      </c>
+      <c r="H19" t="n">
         <v>44.94118</v>
       </c>
-      <c r="G19" t="n">
+      <c r="I19" t="n">
         <v>74.25</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>36.575</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>91.24200000000002</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>35.9425</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>64.39</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>61.642</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>60.422835</v>
       </c>
     </row>
@@ -1449,30 +1567,36 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.36872</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-76.47902000000001</v>
+      </c>
+      <c r="H20" t="n">
         <v>48.58808551724138</v>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
         <v>49</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>45.91249999999999</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>60.1065</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>64.2</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>54.56</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>76.89</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>87.1318</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>60.79861068965517</v>
       </c>
     </row>
@@ -1501,30 +1625,36 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.473698</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-76.469139</v>
+      </c>
+      <c r="H21" t="n">
         <v>44.41324275862069</v>
       </c>
-      <c r="G21" t="n">
+      <c r="I21" t="n">
         <v>74.25</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>52.65000000000001</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>82.917</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>69.2</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>36.65750000000001</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>65.75999999999999</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>61.642</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>60.93621784482759</v>
       </c>
     </row>
@@ -1553,30 +1683,36 @@
         </is>
       </c>
       <c r="F22" t="n">
+        <v>2.4723817</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-76.491625</v>
+      </c>
+      <c r="H22" t="n">
         <v>63.68767448275863</v>
       </c>
-      <c r="G22" t="n">
+      <c r="I22" t="n">
         <v>34.5</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>60.9</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>65.934</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>64.2</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>66.99000000000001</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>60.58499999999999</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>83.3</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>62.51208431034483</v>
       </c>
     </row>
@@ -1605,30 +1741,36 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>2.225754</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-76.270785</v>
+      </c>
+      <c r="H23" t="n">
         <v>62.0009427586207</v>
       </c>
-      <c r="G23" t="n">
+      <c r="I23" t="n">
         <v>67.75</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>55.90000000000001</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>57.276</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>54</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>51.92</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>80.27</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>74.3036</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>62.92756784482759</v>
       </c>
     </row>
@@ -1657,30 +1799,36 @@
         </is>
       </c>
       <c r="F24" t="n">
+        <v>2.276218055</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-76.44762796000001</v>
+      </c>
+      <c r="H24" t="n">
         <v>47.01698137931035</v>
       </c>
-      <c r="G24" t="n">
+      <c r="I24" t="n">
         <v>74.25</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>48.09999999999999</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>82.917</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>59</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>44.165</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>76.66</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>74.30359999999999</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>63.3015726724138</v>
       </c>
     </row>
@@ -1709,30 +1857,36 @@
         </is>
       </c>
       <c r="F25" t="n">
+        <v>2.225453</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-76.27169600000001</v>
+      </c>
+      <c r="H25" t="n">
         <v>60.69160344827586</v>
       </c>
-      <c r="G25" t="n">
+      <c r="I25" t="n">
         <v>67.75</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>62.725</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>74.25900000000001</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>59</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>53.35</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>75.03</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>57.64359999999999</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>63.80615043103448</v>
       </c>
     </row>
@@ -1761,30 +1915,36 @@
         </is>
       </c>
       <c r="F26" t="n">
+        <v>2.338028</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-76.49555700000001</v>
+      </c>
+      <c r="H26" t="n">
         <v>65.35940896551725</v>
       </c>
-      <c r="G26" t="n">
+      <c r="I26" t="n">
         <v>67.75</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>58.60000000000001</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>32.634</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>57.915</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>77.34</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>69.97199999999999</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>64.27130112068966</v>
       </c>
     </row>
@@ -1813,30 +1973,36 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>2.2049957463188</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-76.49610436392901</v>
+      </c>
+      <c r="H27" t="n">
         <v>60.1169</v>
       </c>
-      <c r="G27" t="n">
+      <c r="I27" t="n">
         <v>55.25</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>60.64575000000001</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>96.13377</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>67.77600000000001</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>34.5675</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>68.77</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>74.30359999999999</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>64.69544</v>
       </c>
     </row>
@@ -1865,30 +2031,36 @@
         </is>
       </c>
       <c r="F28" t="n">
+        <v>2.472335</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-76.491513</v>
+      </c>
+      <c r="H28" t="n">
         <v>64.96913724137931</v>
       </c>
-      <c r="G28" t="n">
+      <c r="I28" t="n">
         <v>67.75</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>55.90000000000001</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>65.934</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>59</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>50.2975</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>78.52</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>78.6352</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>65.12572965517242</v>
       </c>
     </row>
@@ -1917,30 +2089,36 @@
         </is>
       </c>
       <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
         <v>60.53436137931035</v>
       </c>
-      <c r="G29" t="n">
+      <c r="I29" t="n">
         <v>74.25</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>63.41250000000001</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>87.07950000000001</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>71.80000000000001</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>43.58750000000001</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>72.27</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>49.147</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>65.2601076724138</v>
       </c>
     </row>
@@ -1969,30 +2147,36 @@
         </is>
       </c>
       <c r="F30" t="n">
+        <v>2.36733519613</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-76.4555627555</v>
+      </c>
+      <c r="H30" t="n">
         <v>63.89185448275862</v>
       </c>
-      <c r="G30" t="n">
+      <c r="I30" t="n">
         <v>67.75</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>52.65000000000001</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>74.25900000000001</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>46.2</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>70.95</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>78.6352</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>65.46700681034483</v>
       </c>
     </row>
@@ -2021,30 +2205,36 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>2.149605187</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-76.48452872999999</v>
+      </c>
+      <c r="H31" t="n">
         <v>69.36642000000001</v>
       </c>
-      <c r="G31" t="n">
+      <c r="I31" t="n">
         <v>61.5</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>58.60000000000001</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>89.62029000000001</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>65.93400000000001</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>36.025</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>69.58</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>74.47019999999999</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>65.63698875</v>
       </c>
     </row>
@@ -2073,30 +2263,36 @@
         </is>
       </c>
       <c r="F32" t="n">
+        <v>2.32329047542</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-76.5120380866</v>
+      </c>
+      <c r="H32" t="n">
         <v>43.98015448275862</v>
       </c>
-      <c r="G32" t="n">
+      <c r="I32" t="n">
         <v>61.5</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>52.65</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>82.917</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>69.2</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>51.1775</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>81.48999999999999</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>82.8002</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>65.71435681034482</v>
       </c>
     </row>
@@ -2125,30 +2321,36 @@
         </is>
       </c>
       <c r="F33" t="n">
+        <v>2.428444</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-76.510417</v>
+      </c>
+      <c r="H33" t="n">
         <v>47.87783448275862</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>61.5</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>83.72499999999999</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>91.242</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>59.10000000000001</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>59.345</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>70.97</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>53.4786</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>65.90480431034484</v>
       </c>
     </row>
@@ -2177,30 +2379,36 @@
         </is>
       </c>
       <c r="F34" t="n">
+        <v>2.439094</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-76.45004400000001</v>
+      </c>
+      <c r="H34" t="n">
         <v>65.26936827586208</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>59.935</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>65</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>49.617</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>64.2</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>52.36</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>80.34</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>91.46339999999999</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>66.02309603448276</v>
       </c>
     </row>
@@ -2229,30 +2437,36 @@
         </is>
       </c>
       <c r="F35" t="n">
+        <v>2.224887</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-76.272627</v>
+      </c>
+      <c r="H35" t="n">
         <v>64.06455172413794</v>
       </c>
-      <c r="G35" t="n">
+      <c r="I35" t="n">
         <v>67.75</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>70.95</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>62.271</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>49.83</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>82.98999999999999</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>57.81019999999999</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>66.25821896551724</v>
       </c>
     </row>
@@ -2281,30 +2495,36 @@
         </is>
       </c>
       <c r="F36" t="n">
+        <v>2.3394663976658</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-76.496900203641</v>
+      </c>
+      <c r="H36" t="n">
         <v>85.88216068965518</v>
       </c>
-      <c r="G36" t="n">
+      <c r="I36" t="n">
         <v>63.585</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>60.45</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>65.934</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>39.2</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>52.4425</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>85.47</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>87.13179999999998</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>67.5119325862069</v>
       </c>
     </row>
@@ -2333,30 +2553,36 @@
         </is>
       </c>
       <c r="F37" t="n">
+        <v>2.327291821</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-76.32101373</v>
+      </c>
+      <c r="H37" t="n">
         <v>77.3991027586207</v>
       </c>
-      <c r="G37" t="n">
+      <c r="I37" t="n">
         <v>80.5</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>51.52500000000001</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>44.4888</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>64.2</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>57.42</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>87.1318</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>67.63308784482759</v>
       </c>
     </row>
@@ -2385,30 +2611,36 @@
         </is>
       </c>
       <c r="F38" t="n">
+        <v>2.2016518</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-76.5200358</v>
+      </c>
+      <c r="H38" t="n">
         <v>63.95819724137932</v>
       </c>
-      <c r="G38" t="n">
+      <c r="I38" t="n">
         <v>55.25</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>71.2</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>97.01289</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
         <v>49.19750000000001</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>61.84</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>74.47019999999999</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>68.41609840517241</v>
       </c>
     </row>
@@ -2437,30 +2669,36 @@
         </is>
       </c>
       <c r="F39" t="n">
+        <v>4.7133</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-74.1302</v>
+      </c>
+      <c r="H39" t="n">
         <v>63.36391724137931</v>
       </c>
-      <c r="G39" t="n">
+      <c r="I39" t="n">
         <v>67.75</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>79.93275</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>63.51309000000001</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>71.32000000000001</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>49.005</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>80.15000000000001</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>74.3036</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>68.66729465517241</v>
       </c>
     </row>
@@ -2489,30 +2727,36 @@
         </is>
       </c>
       <c r="F40" t="n">
+        <v>2.4596723</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-76.5071897</v>
+      </c>
+      <c r="H40" t="n">
         <v>48.43382</v>
       </c>
-      <c r="G40" t="n">
+      <c r="I40" t="n">
         <v>80.75</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>77.95</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>91.24200000000002</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>66.80000000000001</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>48.4</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>76.95999999999999</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>65.97359999999999</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>69.5636775</v>
       </c>
     </row>
@@ -2541,30 +2785,36 @@
         </is>
       </c>
       <c r="F41" t="n">
+        <v>2.309844049</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-76.50303323999999</v>
+      </c>
+      <c r="H41" t="n">
         <v>61.04821724137931</v>
       </c>
-      <c r="G41" t="n">
+      <c r="I41" t="n">
         <v>80.75</v>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>57.2</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>65.934</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>70.93400000000001</v>
       </c>
-      <c r="K41" t="n">
+      <c r="M41" t="n">
         <v>58.8775</v>
       </c>
-      <c r="L41" t="n">
+      <c r="N41" t="n">
         <v>81.42</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>82.8002</v>
       </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
         <v>69.87048965517242</v>
       </c>
     </row>
@@ -2593,30 +2843,36 @@
         </is>
       </c>
       <c r="F42" t="n">
+        <v>2.4030416491654</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-76.497754581858</v>
+      </c>
+      <c r="H42" t="n">
         <v>64.74143103448277</v>
       </c>
-      <c r="G42" t="n">
+      <c r="I42" t="n">
         <v>56.29</v>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>73.18275</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>81.36189000000002</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>67.66600000000001</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>61.325</v>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>80.00999999999999</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>82.8002</v>
       </c>
-      <c r="N42" t="n">
+      <c r="P42" t="n">
         <v>70.92215887931035</v>
       </c>
     </row>
@@ -2645,30 +2901,36 @@
         </is>
       </c>
       <c r="F43" t="n">
+        <v>2.329504</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-76.460082</v>
+      </c>
+      <c r="H43" t="n">
         <v>65.72913103448276</v>
       </c>
-      <c r="G43" t="n">
+      <c r="I43" t="n">
         <v>70.34999999999999</v>
       </c>
-      <c r="H43" t="n">
+      <c r="J43" t="n">
         <v>83.90000000000001</v>
       </c>
-      <c r="I43" t="n">
+      <c r="K43" t="n">
         <v>55.27800000000001</v>
       </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
         <v>69.33199999999999</v>
       </c>
-      <c r="K43" t="n">
+      <c r="M43" t="n">
         <v>62.92</v>
       </c>
-      <c r="L43" t="n">
+      <c r="N43" t="n">
         <v>86.66</v>
       </c>
-      <c r="M43" t="n">
+      <c r="O43" t="n">
         <v>86.9652</v>
       </c>
-      <c r="N43" t="n">
+      <c r="P43" t="n">
         <v>72.64179137931035</v>
       </c>
     </row>
@@ -2697,30 +2959,36 @@
         </is>
       </c>
       <c r="F44" t="n">
+        <v>2.430869</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-76.59200300000001</v>
+      </c>
+      <c r="H44" t="n">
         <v>63.96483724137931</v>
       </c>
-      <c r="G44" t="n">
+      <c r="I44" t="n">
         <v>100</v>
       </c>
-      <c r="H44" t="n">
+      <c r="J44" t="n">
         <v>82.67500000000001</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>85.69089</v>
       </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
         <v>82.866</v>
       </c>
-      <c r="K44" t="n">
+      <c r="M44" t="n">
         <v>47.74</v>
       </c>
-      <c r="L44" t="n">
+      <c r="N44" t="n">
         <v>65.16</v>
       </c>
-      <c r="M44" t="n">
+      <c r="O44" t="n">
         <v>74.3036</v>
       </c>
-      <c r="N44" t="n">
+      <c r="P44" t="n">
         <v>75.30004090517241</v>
       </c>
     </row>
@@ -2749,30 +3017,36 @@
         </is>
       </c>
       <c r="F45" t="n">
+        <v>2.2053</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-76.30029999999999</v>
+      </c>
+      <c r="H45" t="n">
         <v>77.75090827586207</v>
       </c>
-      <c r="G45" t="n">
+      <c r="I45" t="n">
         <v>80.5</v>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>67.8</v>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>75.45780000000001</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>75.44</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
         <v>53.13</v>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
         <v>72.45999999999999</v>
       </c>
-      <c r="M45" t="n">
+      <c r="O45" t="n">
         <v>99.95999999999999</v>
       </c>
-      <c r="N45" t="n">
+      <c r="P45" t="n">
         <v>75.31233853448276</v>
       </c>
     </row>
@@ -2801,30 +3075,36 @@
         </is>
       </c>
       <c r="F46" t="n">
+        <v>2.4448969135393</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-76.603289566914</v>
+      </c>
+      <c r="H46" t="n">
         <v>69.72835724137931</v>
       </c>
-      <c r="G46" t="n">
+      <c r="I46" t="n">
         <v>50</v>
       </c>
-      <c r="H46" t="n">
+      <c r="J46" t="n">
         <v>96.88325</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
         <v>93.04353</v>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
         <v>64.58200000000001</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
         <v>59.3725</v>
       </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
         <v>78.97</v>
       </c>
-      <c r="M46" t="n">
+      <c r="O46" t="n">
         <v>91.46339999999999</v>
       </c>
-      <c r="N46" t="n">
+      <c r="P46" t="n">
         <v>75.5053796551724</v>
       </c>
     </row>
